--- a/config/generated/templates/TraceNode.xlsx
+++ b/config/generated/templates/TraceNode.xlsx
@@ -43,7 +43,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>ff888797ba13c3d4</t>
+    <t>eaebfd9280ebc095</t>
   </si>
   <si>
     <t>#name</t>
@@ -79,7 +79,7 @@
     <t>i32</t>
   </si>
   <si>
-    <t>list&lt;ref&lt;TraceNode.id&gt;&gt;</t>
+    <t>optional&lt;list&lt;ref&lt;TraceNode.id&gt;&gt;&gt;</t>
   </si>
   <si>
     <t>#scope</t>
@@ -522,7 +522,7 @@
     <col min="3" max="3" width="17.7109375" style="5" customWidth="1"/>
     <col min="4" max="4" width="19.7109375" style="5" customWidth="1"/>
     <col min="5" max="5" width="21.7109375" style="5" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="32.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">

--- a/config/generated/templates/TraceNode.xlsx
+++ b/config/generated/templates/TraceNode.xlsx
@@ -34,16 +34,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>eaebfd9280ebc095</t>
+    <t>1dc49f28618805b9</t>
   </si>
   <si>
     <t>#name</t>
@@ -82,7 +82,7 @@
     <t>optional&lt;list&lt;ref&lt;TraceNode.id&gt;&gt;&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
